--- a/apps/web/public/templates/03_الشركات.xlsx
+++ b/apps/web/public/templates/03_الشركات.xlsx
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"الشركات": [["CO-BRIDGE", "بريدج", "شركة بريدج للهندسة والمقاولات", "", "", "invoices@bridge.com", "", ""]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/apps/web/public/templates/03_الشركات.xlsx
+++ b/apps/web/public/templates/03_الشركات.xlsx
@@ -532,7 +532,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>كود الشركة *</t>
+          <t>كود الشركة المنفذة *</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>إيميل المستخلصات *</t>
+          <t>البريد الإلكتروني للمستخلصات *</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>التليفون</t>
+          <t>رقم الهاتف</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
@@ -659,21 +659,21 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>قالب الشركات المنفذة</t>
+          <t>نموذج الشركات المنفذة</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>الغرض: تعريف الشركات المنفذة.</t>
+          <t>الغرض: تعريف الشركات المنفذة (المقاولين).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>مين بيرفعه: مدير النظام.</t>
+          <t>الجهة المسؤولة عن الرفع: مدير النظام.</t>
         </is>
       </c>
     </row>
@@ -683,14 +683,14 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>• الإيميل ده اللي بيوصله إشعار الصرف وجاهزية الشيك.</t>
+          <t>• يُرسل إلى هذا البريد الإلكتروني تنبيه السداد وجاهزية الشيك.</t>
         </is>
       </c>
     </row>
@@ -700,49 +700,49 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>

--- a/apps/web/public/templates/03_الشركات.xlsx
+++ b/apps/web/public/templates/03_الشركات.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>بريدج</t>
+          <t>مثال — بريدج</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"الشركات": [["CO-BRIDGE", "بريدج", "شركة بريدج للهندسة والمقاولات", "", "", "invoices@bridge.com", "", ""]]}</t>
+          <t>{"الشركات": [["CO-BRIDGE", "مثال — بريدج", "شركة بريدج للهندسة والمقاولات", "", "", "invoices@bridge.com", "", ""]]}</t>
         </is>
       </c>
     </row>
